--- a/Train Automation System/Grading/2 stage/6-examples/Train-Automation-System_Grading_2-stage_2026-03-12_6-examples_CombinedHumanGradingVsClaude4.5SonnetAutoGrading_Claude4.5SonnetGeneration.xlsx
+++ b/Train Automation System/Grading/2 stage/6-examples/Train-Automation-System_Grading_2-stage_2026-03-12_6-examples_CombinedHumanGradingVsClaude4.5SonnetAutoGrading_Claude4.5SonnetGeneration.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/marc-antoinenadeau/Desktop/Evaluations 2/Train Automation System/Grading/2 stage/2026-03-12/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/marc-antoinenadeau/Desktop/B.Eng Software Engineering /7th Semester/Capstone/Code/Evaluations/Train Automation System/Grading/2 stage/6-examples/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{548396B5-9B5C-3449-85D2-FD299D4ECC27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{067248BD-68F0-584F-8D97-3CA2B195BDA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17480" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17280" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Train Automation System" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="774" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="774" uniqueCount="212">
   <si>
     <t>Type</t>
   </si>
@@ -316,16 +316,10 @@
     <t>StoppedAtStation exists but represents intermediate stations; WaitingAtFirstStation represents first station</t>
   </si>
   <si>
-    <t>Entry Action</t>
-  </si>
-  <si>
     <t>openDoors()</t>
   </si>
   <si>
     <t>DoorsOpening state with entry/openDoors() in StoppedAtStation composite</t>
-  </si>
-  <si>
-    <t>Exit Action</t>
   </si>
   <si>
     <t>closeDoors()</t>
@@ -1268,14 +1262,14 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -12696,30 +12690,30 @@
     </row>
     <row r="11" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="C11" s="14">
+        <v>1</v>
+      </c>
+      <c r="D11" s="15" t="s">
         <v>92</v>
-      </c>
-      <c r="C11" s="14">
-        <v>1</v>
-      </c>
-      <c r="D11" s="15" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="11" t="s">
-        <v>94</v>
+        <v>9</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C12" s="4">
         <v>0.5</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -12733,7 +12727,7 @@
         <v>0.5</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -12747,7 +12741,7 @@
         <v>1</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -12761,7 +12755,7 @@
         <v>0.5</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -12775,7 +12769,7 @@
         <v>1</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.15">
@@ -12789,7 +12783,7 @@
         <v>1</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="5"/>
@@ -12821,21 +12815,21 @@
         <v>0</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="13" t="s">
-        <v>91</v>
+        <v>9</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C19" s="14">
         <v>0.5</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="20" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -12849,7 +12843,7 @@
         <v>0.5</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="21" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -12863,7 +12857,7 @@
         <v>1</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="22" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -12877,7 +12871,7 @@
         <v>0</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="23" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -12891,7 +12885,7 @@
         <v>1</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
@@ -12923,7 +12917,7 @@
         <v>1</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="25" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -12937,7 +12931,7 @@
         <v>1</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="26" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.15">
@@ -12951,7 +12945,7 @@
         <v>0</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="27" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -12965,7 +12959,7 @@
         <v>1</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="28" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -12979,21 +12973,21 @@
         <v>0</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="29" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="13" t="s">
-        <v>91</v>
+        <v>9</v>
       </c>
       <c r="B29" s="14" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C29" s="14">
         <v>1</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="30" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -13007,7 +13001,7 @@
         <v>0</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E30" s="5"/>
       <c r="F30" s="5"/>
@@ -13039,7 +13033,7 @@
         <v>1</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E31" s="5"/>
       <c r="F31" s="5"/>
@@ -13071,7 +13065,7 @@
         <v>0.5</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="33" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -13085,21 +13079,21 @@
         <v>0</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="34" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="11" t="s">
-        <v>91</v>
+        <v>9</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C34" s="4">
         <v>1</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="35" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -13113,7 +13107,7 @@
         <v>0</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="36" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -13127,7 +13121,7 @@
         <v>1</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="37" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -13141,7 +13135,7 @@
         <v>1</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="38" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.15">
@@ -13155,7 +13149,7 @@
         <v>1</v>
       </c>
       <c r="D38" s="15" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E38" s="5"/>
       <c r="F38" s="5"/>
@@ -13187,7 +13181,7 @@
         <v>1</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E39" s="5"/>
       <c r="F39" s="5"/>
@@ -13219,7 +13213,7 @@
         <v>1</v>
       </c>
       <c r="D40" s="15" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E40" s="5"/>
       <c r="F40" s="5"/>
@@ -13251,7 +13245,7 @@
         <v>1</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E41" s="5"/>
       <c r="F41" s="5"/>
@@ -13283,7 +13277,7 @@
         <v>1</v>
       </c>
       <c r="D42" s="15" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E42" s="5"/>
       <c r="F42" s="5"/>
@@ -13315,7 +13309,7 @@
         <v>1</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E43" s="5"/>
       <c r="F43" s="5"/>
@@ -13347,7 +13341,7 @@
         <v>1</v>
       </c>
       <c r="D44" s="15" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E44" s="5"/>
       <c r="F44" s="5"/>
@@ -13379,7 +13373,7 @@
         <v>0.5</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E45" s="5"/>
       <c r="F45" s="5"/>
@@ -13411,7 +13405,7 @@
         <v>0.5</v>
       </c>
       <c r="D46" s="15" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E46" s="5"/>
       <c r="F46" s="5"/>
@@ -13443,7 +13437,7 @@
         <v>1</v>
       </c>
       <c r="D47" s="12" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E47" s="5"/>
       <c r="F47" s="5"/>
@@ -13475,7 +13469,7 @@
         <v>0.5</v>
       </c>
       <c r="D48" s="15" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -13489,7 +13483,7 @@
         <v>1</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -13503,7 +13497,7 @@
         <v>0</v>
       </c>
       <c r="D50" s="15" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -13517,7 +13511,7 @@
         <v>0</v>
       </c>
       <c r="D51" s="12" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -13531,7 +13525,7 @@
         <v>0</v>
       </c>
       <c r="D52" s="15" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -13545,7 +13539,7 @@
         <v>0</v>
       </c>
       <c r="D53" s="12" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -13559,7 +13553,7 @@
         <v>0.5</v>
       </c>
       <c r="D54" s="15" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -13573,7 +13567,7 @@
         <v>0</v>
       </c>
       <c r="D55" s="12" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -13587,7 +13581,7 @@
         <v>0.5</v>
       </c>
       <c r="D56" s="15" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -13601,7 +13595,7 @@
         <v>0</v>
       </c>
       <c r="D57" s="12" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -13615,7 +13609,7 @@
         <v>0</v>
       </c>
       <c r="D58" s="15" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -13629,7 +13623,7 @@
         <v>0</v>
       </c>
       <c r="D59" s="12" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -13643,7 +13637,7 @@
         <v>0.5</v>
       </c>
       <c r="D60" s="15" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -13657,7 +13651,7 @@
         <v>0.5</v>
       </c>
       <c r="D61" s="19" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -13671,7 +13665,7 @@
         <v>0</v>
       </c>
       <c r="D62" s="19" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -13685,7 +13679,7 @@
         <v>1</v>
       </c>
       <c r="D63" s="19" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -13699,7 +13693,7 @@
         <v>1</v>
       </c>
       <c r="D64" s="19" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -13713,7 +13707,7 @@
         <v>1</v>
       </c>
       <c r="D65" s="19" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -13727,7 +13721,7 @@
         <v>1</v>
       </c>
       <c r="D66" s="19" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -13741,7 +13735,7 @@
         <v>0.5</v>
       </c>
       <c r="D67" s="19" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -13755,7 +13749,7 @@
         <v>0.5</v>
       </c>
       <c r="D68" s="19" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -13769,7 +13763,7 @@
         <v>1</v>
       </c>
       <c r="D69" s="19" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -13783,7 +13777,7 @@
         <v>0.5</v>
       </c>
       <c r="D70" s="19" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -13797,7 +13791,7 @@
         <v>0</v>
       </c>
       <c r="D71" s="19" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -13811,7 +13805,7 @@
         <v>0</v>
       </c>
       <c r="D72" s="21" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="73" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -13825,7 +13819,7 @@
         <v>0</v>
       </c>
       <c r="D73" s="15" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="74" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -13839,7 +13833,7 @@
         <v>0</v>
       </c>
       <c r="D74" s="12" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -13853,7 +13847,7 @@
         <v>0</v>
       </c>
       <c r="D75" s="12" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -13867,7 +13861,7 @@
         <v>0</v>
       </c>
       <c r="D76" s="12" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="77" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -13881,7 +13875,7 @@
         <v>0</v>
       </c>
       <c r="D77" s="12" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -13895,7 +13889,7 @@
         <v>0</v>
       </c>
       <c r="D78" s="12" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="79" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -18581,18 +18575,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="68" t="s">
-        <v>161</v>
-      </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="69"/>
-      <c r="D1" s="69"/>
-      <c r="E1" s="69"/>
-      <c r="F1" s="69"/>
-      <c r="G1" s="69"/>
-      <c r="H1" s="69"/>
+      <c r="A1" s="70" t="s">
+        <v>159</v>
+      </c>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
+      <c r="H1" s="71"/>
       <c r="J1" s="22" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -18600,28 +18594,28 @@
         <v>0</v>
       </c>
       <c r="B2" s="23" t="s">
+        <v>161</v>
+      </c>
+      <c r="C2" s="23" t="s">
+        <v>162</v>
+      </c>
+      <c r="D2" s="23" t="s">
         <v>163</v>
       </c>
-      <c r="C2" s="23" t="s">
+      <c r="E2" s="23" t="s">
         <v>164</v>
       </c>
-      <c r="D2" s="23" t="s">
+      <c r="F2" s="23" t="s">
         <v>165</v>
       </c>
-      <c r="E2" s="23" t="s">
+      <c r="G2" s="23" t="s">
         <v>166</v>
       </c>
-      <c r="F2" s="23" t="s">
+      <c r="H2" s="23" t="s">
         <v>167</v>
       </c>
-      <c r="G2" s="23" t="s">
+      <c r="J2" s="24" t="s">
         <v>168</v>
-      </c>
-      <c r="H2" s="23" t="s">
-        <v>169</v>
-      </c>
-      <c r="J2" s="24" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -18691,7 +18685,7 @@
         <v>0.92063492063492058</v>
       </c>
       <c r="J4" s="22" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -18727,7 +18721,7 @@
         <v>0.93333333333333335</v>
       </c>
       <c r="J5" s="24" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -18864,7 +18858,7 @@
     </row>
     <row r="10" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="28" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B10" s="26">
         <f t="shared" ref="B10:E10" si="3">SUM(B3:B9)</f>
@@ -18906,46 +18900,46 @@
       <c r="H11" s="27"/>
     </row>
     <row r="12" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="68" t="s">
-        <v>174</v>
-      </c>
-      <c r="B12" s="69"/>
-      <c r="C12" s="69"/>
-      <c r="D12" s="69"/>
-      <c r="E12" s="69"/>
-      <c r="F12" s="69"/>
-      <c r="G12" s="69"/>
-      <c r="H12" s="69"/>
+      <c r="A12" s="70" t="s">
+        <v>172</v>
+      </c>
+      <c r="B12" s="71"/>
+      <c r="C12" s="71"/>
+      <c r="D12" s="71"/>
+      <c r="E12" s="71"/>
+      <c r="F12" s="71"/>
+      <c r="G12" s="71"/>
+      <c r="H12" s="71"/>
     </row>
     <row r="13" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="23" t="s">
         <v>0</v>
       </c>
       <c r="B13" s="23" t="s">
+        <v>161</v>
+      </c>
+      <c r="C13" s="23" t="s">
+        <v>162</v>
+      </c>
+      <c r="D13" s="23" t="s">
         <v>163</v>
       </c>
-      <c r="C13" s="23" t="s">
+      <c r="E13" s="23" t="s">
         <v>164</v>
       </c>
-      <c r="D13" s="23" t="s">
+      <c r="F13" s="23" t="s">
         <v>165</v>
       </c>
-      <c r="E13" s="23" t="s">
+      <c r="G13" s="23" t="s">
         <v>166</v>
       </c>
-      <c r="F13" s="23" t="s">
+      <c r="H13" s="23" t="s">
         <v>167</v>
-      </c>
-      <c r="G13" s="23" t="s">
-        <v>168</v>
-      </c>
-      <c r="H13" s="23" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="25" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B14" s="26">
         <f>COUNTIF('Train Automation System'!$A$2:$A$71, A14)</f>
@@ -19052,7 +19046,7 @@
       </c>
       <c r="C17" s="26">
         <f>SUMIF('LLM Grading'!$A$2:$A$71, $A17, 'LLM Grading'!$C$2:$C$71)</f>
-        <v>4.5</v>
+        <v>8.5</v>
       </c>
       <c r="D17" s="26">
         <f>SUMIF('LLM Grading'!$A$72:$A$78, $A17, 'LLM Grading'!$C$72:$C$78)</f>
@@ -19068,11 +19062,11 @@
       </c>
       <c r="G17" s="26">
         <f t="shared" si="5"/>
-        <v>0.375</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="H17" s="26">
         <f t="shared" si="6"/>
-        <v>0.54545454545454541</v>
+        <v>0.82926829268292679</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -19176,7 +19170,7 @@
     </row>
     <row r="21" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="28" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B21" s="29">
         <f t="shared" ref="B21:E21" si="7">SUM(B14:B20)</f>
@@ -19184,7 +19178,7 @@
       </c>
       <c r="C21" s="29">
         <f t="shared" si="7"/>
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D21" s="29">
         <f t="shared" si="7"/>
@@ -19200,11 +19194,11 @@
       </c>
       <c r="G21" s="26">
         <f t="shared" si="5"/>
-        <v>0.51428571428571423</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="H21" s="30">
         <f t="shared" si="6"/>
-        <v>0.67924528301886788</v>
+        <v>0.72727272727272729</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -20230,20 +20224,20 @@
         <v>1</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E1" s="32"/>
-      <c r="F1" s="70" t="s">
-        <v>176</v>
-      </c>
-      <c r="G1" s="71"/>
-      <c r="H1" s="71"/>
-      <c r="I1" s="71"/>
+      <c r="F1" s="68" t="s">
+        <v>174</v>
+      </c>
+      <c r="G1" s="69"/>
+      <c r="H1" s="69"/>
+      <c r="I1" s="69"/>
       <c r="L1" s="72" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="M1" s="73"/>
       <c r="N1" s="73"/>
@@ -20267,29 +20261,29 @@
       </c>
       <c r="E2" s="32"/>
       <c r="F2" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="G2" s="34" t="s">
+        <v>177</v>
+      </c>
+      <c r="H2" s="35" t="s">
         <v>178</v>
       </c>
-      <c r="G2" s="34" t="s">
+      <c r="I2" s="36" t="s">
         <v>179</v>
       </c>
-      <c r="H2" s="35" t="s">
+      <c r="J2" s="37" t="s">
         <v>180</v>
-      </c>
-      <c r="I2" s="36" t="s">
-        <v>181</v>
-      </c>
-      <c r="J2" s="37" t="s">
-        <v>182</v>
       </c>
       <c r="K2" s="9"/>
       <c r="L2" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="M2" s="38" t="s">
+        <v>182</v>
+      </c>
+      <c r="N2" s="38" t="s">
         <v>183</v>
-      </c>
-      <c r="M2" s="38" t="s">
-        <v>184</v>
-      </c>
-      <c r="N2" s="38" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -20331,14 +20325,14 @@
       </c>
       <c r="K3" s="9"/>
       <c r="L3" s="43" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="M3" s="40">
         <f>(G3+H4+I5)/COUNTA($C$2:$C$125)</f>
         <v>0.5714285714285714</v>
       </c>
       <c r="N3" s="42" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -20380,14 +20374,14 @@
       </c>
       <c r="K4" s="9"/>
       <c r="L4" s="43" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="M4" s="44">
         <f t="array" ref="M4">SUMPRODUCT(J3:J5/COUNTA($C$2:$C$125), TRANSPOSE(G6:I6)/COUNTA($C$2:$C$125))</f>
         <v>0.36633496373756114</v>
       </c>
       <c r="N4" s="45" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -20429,14 +20423,14 @@
       </c>
       <c r="K5" s="9"/>
       <c r="L5" s="43" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="M5" s="46">
         <f>(M3-M4)/(1-M4)</f>
         <v>0.32366249667287728</v>
       </c>
       <c r="N5" s="48" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -20458,7 +20452,7 @@
       </c>
       <c r="E6" s="32"/>
       <c r="F6" s="49" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="G6" s="9">
         <f t="shared" ref="G6:I6" si="2">SUM(G3:G5)</f>
@@ -20516,14 +20510,14 @@
         <v>1</v>
       </c>
       <c r="E8" s="32"/>
-      <c r="F8" s="70" t="s">
-        <v>192</v>
-      </c>
-      <c r="G8" s="71"/>
-      <c r="H8" s="71"/>
-      <c r="I8" s="71"/>
+      <c r="F8" s="68" t="s">
+        <v>190</v>
+      </c>
+      <c r="G8" s="69"/>
+      <c r="H8" s="69"/>
+      <c r="I8" s="69"/>
       <c r="L8" s="72" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="M8" s="73"/>
       <c r="N8" s="73"/>
@@ -20550,26 +20544,26 @@
         <v>4</v>
       </c>
       <c r="G9" s="51" t="s">
+        <v>177</v>
+      </c>
+      <c r="H9" s="51" t="s">
+        <v>178</v>
+      </c>
+      <c r="I9" s="51" t="s">
         <v>179</v>
       </c>
-      <c r="H9" s="51" t="s">
+      <c r="J9" s="52" t="s">
         <v>180</v>
-      </c>
-      <c r="I9" s="51" t="s">
-        <v>181</v>
-      </c>
-      <c r="J9" s="52" t="s">
-        <v>182</v>
       </c>
       <c r="K9" s="9"/>
       <c r="L9" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="M9" s="38" t="s">
+        <v>182</v>
+      </c>
+      <c r="N9" s="38" t="s">
         <v>183</v>
-      </c>
-      <c r="M9" s="38" t="s">
-        <v>184</v>
-      </c>
-      <c r="N9" s="38" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -20611,14 +20605,14 @@
       </c>
       <c r="K10" s="9"/>
       <c r="L10" s="43" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="M10" s="40">
         <f>(G10+H11+I12)/COUNTIF($A$2:$A$125,F9)</f>
         <v>0.44444444444444442</v>
       </c>
       <c r="N10" s="42" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -20660,14 +20654,14 @@
       </c>
       <c r="K11" s="9"/>
       <c r="L11" s="43" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="M11" s="44">
         <f t="array" ref="M11">SUMPRODUCT(J10:J12/COUNTIF($A$2:$A$125,F9), TRANSPOSE(G13:I13)/COUNTIF($A$2:$A$125,F9))</f>
         <v>0.3179012345679012</v>
       </c>
       <c r="N11" s="45" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -20709,14 +20703,14 @@
       </c>
       <c r="K12" s="9"/>
       <c r="L12" s="43" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="M12" s="46">
         <f>(M10-M11)/(1-M11)</f>
         <v>0.18552036199095023</v>
       </c>
       <c r="N12" s="48" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -20738,7 +20732,7 @@
       </c>
       <c r="E13" s="32"/>
       <c r="F13" s="49" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="G13" s="9">
         <f t="shared" ref="G13:I13" si="6">SUM(G10:G12)</f>
@@ -20793,14 +20787,14 @@
         <v>0.5</v>
       </c>
       <c r="E15" s="32"/>
-      <c r="F15" s="70" t="s">
-        <v>194</v>
-      </c>
-      <c r="G15" s="71"/>
-      <c r="H15" s="71"/>
-      <c r="I15" s="71"/>
+      <c r="F15" s="68" t="s">
+        <v>192</v>
+      </c>
+      <c r="G15" s="69"/>
+      <c r="H15" s="69"/>
+      <c r="I15" s="69"/>
       <c r="L15" s="72" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="M15" s="73"/>
       <c r="N15" s="73"/>
@@ -20827,26 +20821,26 @@
         <v>7</v>
       </c>
       <c r="G16" s="51" t="s">
+        <v>177</v>
+      </c>
+      <c r="H16" s="51" t="s">
+        <v>178</v>
+      </c>
+      <c r="I16" s="51" t="s">
         <v>179</v>
       </c>
-      <c r="H16" s="51" t="s">
+      <c r="J16" s="52" t="s">
         <v>180</v>
-      </c>
-      <c r="I16" s="51" t="s">
-        <v>181</v>
-      </c>
-      <c r="J16" s="52" t="s">
-        <v>182</v>
       </c>
       <c r="K16" s="9"/>
       <c r="L16" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="M16" s="38" t="s">
+        <v>182</v>
+      </c>
+      <c r="N16" s="38" t="s">
         <v>183</v>
-      </c>
-      <c r="M16" s="38" t="s">
-        <v>184</v>
-      </c>
-      <c r="N16" s="38" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -20888,14 +20882,14 @@
       </c>
       <c r="K17" s="9"/>
       <c r="L17" s="43" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="M17" s="40">
         <f>(G17+H18+I19)/COUNTIF($A$2:$A$125,F16)</f>
         <v>0.42857142857142855</v>
       </c>
       <c r="N17" s="42" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -20937,14 +20931,14 @@
       </c>
       <c r="K18" s="9"/>
       <c r="L18" s="43" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="M18" s="44">
         <f t="array" ref="M18">SUMPRODUCT(J17:J19/COUNTIF($A$2:$A$125,F16), TRANSPOSE(G20:I20)/COUNTIF($A$2:$A$125,F16))</f>
         <v>0.32426303854875282</v>
       </c>
       <c r="N18" s="45" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -20986,14 +20980,14 @@
       </c>
       <c r="K19" s="9"/>
       <c r="L19" s="43" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="M19" s="46">
         <f>(M17-M18)/(1-M18)</f>
         <v>0.15436241610738252</v>
       </c>
       <c r="N19" s="48" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -21015,7 +21009,7 @@
       </c>
       <c r="E20" s="32"/>
       <c r="F20" s="49" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="G20" s="9">
         <f t="shared" ref="G20:I20" si="10">SUM(G17:G19)</f>
@@ -21070,14 +21064,14 @@
         <v>0</v>
       </c>
       <c r="E22" s="32"/>
-      <c r="F22" s="70" t="s">
-        <v>196</v>
-      </c>
-      <c r="G22" s="71"/>
-      <c r="H22" s="71"/>
-      <c r="I22" s="71"/>
+      <c r="F22" s="68" t="s">
+        <v>194</v>
+      </c>
+      <c r="G22" s="69"/>
+      <c r="H22" s="69"/>
+      <c r="I22" s="69"/>
       <c r="L22" s="72" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="M22" s="73"/>
       <c r="N22" s="73"/>
@@ -21104,26 +21098,26 @@
         <v>11</v>
       </c>
       <c r="G23" s="51" t="s">
+        <v>177</v>
+      </c>
+      <c r="H23" s="51" t="s">
+        <v>178</v>
+      </c>
+      <c r="I23" s="51" t="s">
         <v>179</v>
       </c>
-      <c r="H23" s="51" t="s">
+      <c r="J23" s="52" t="s">
         <v>180</v>
-      </c>
-      <c r="I23" s="51" t="s">
-        <v>181</v>
-      </c>
-      <c r="J23" s="52" t="s">
-        <v>182</v>
       </c>
       <c r="K23" s="9"/>
       <c r="L23" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="M23" s="38" t="s">
+        <v>182</v>
+      </c>
+      <c r="N23" s="38" t="s">
         <v>183</v>
-      </c>
-      <c r="M23" s="38" t="s">
-        <v>184</v>
-      </c>
-      <c r="N23" s="38" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -21165,14 +21159,14 @@
       </c>
       <c r="K24" s="9"/>
       <c r="L24" s="43" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="M24" s="40">
         <f>(G24+H25+I26)/COUNTIF($A$2:$A$125,F23)</f>
         <v>1</v>
       </c>
       <c r="N24" s="42" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -21214,14 +21208,14 @@
       </c>
       <c r="K25" s="9"/>
       <c r="L25" s="43" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="M25" s="44">
         <f t="array" ref="M25">SUMPRODUCT(J24:J26/COUNTIF($A$2:$A$125,F23), TRANSPOSE(G27:I27)/COUNTIF($A$2:$A$125,F23))</f>
         <v>0.55555555555555558</v>
       </c>
       <c r="N25" s="45" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -21263,14 +21257,14 @@
       </c>
       <c r="K26" s="9"/>
       <c r="L26" s="43" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="M26" s="46">
         <f>(M24-M25)/(1-M25)</f>
         <v>1</v>
       </c>
       <c r="N26" s="48" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -21292,7 +21286,7 @@
       </c>
       <c r="E27" s="32"/>
       <c r="F27" s="49" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="G27" s="9">
         <f t="shared" ref="G27:I27" si="14">SUM(G24:G26)</f>
@@ -21347,14 +21341,14 @@
         <v>1</v>
       </c>
       <c r="E29" s="32"/>
-      <c r="F29" s="70" t="s">
-        <v>198</v>
-      </c>
-      <c r="G29" s="71"/>
-      <c r="H29" s="71"/>
-      <c r="I29" s="71"/>
+      <c r="F29" s="68" t="s">
+        <v>196</v>
+      </c>
+      <c r="G29" s="69"/>
+      <c r="H29" s="69"/>
+      <c r="I29" s="69"/>
       <c r="L29" s="72" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="M29" s="73"/>
       <c r="N29" s="73"/>
@@ -21381,26 +21375,26 @@
         <v>21</v>
       </c>
       <c r="G30" s="51" t="s">
+        <v>177</v>
+      </c>
+      <c r="H30" s="51" t="s">
+        <v>178</v>
+      </c>
+      <c r="I30" s="51" t="s">
         <v>179</v>
       </c>
-      <c r="H30" s="51" t="s">
+      <c r="J30" s="52" t="s">
         <v>180</v>
-      </c>
-      <c r="I30" s="51" t="s">
-        <v>181</v>
-      </c>
-      <c r="J30" s="52" t="s">
-        <v>182</v>
       </c>
       <c r="K30" s="9"/>
       <c r="L30" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="M30" s="38" t="s">
+        <v>182</v>
+      </c>
+      <c r="N30" s="38" t="s">
         <v>183</v>
-      </c>
-      <c r="M30" s="38" t="s">
-        <v>184</v>
-      </c>
-      <c r="N30" s="38" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="31" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -21442,14 +21436,14 @@
       </c>
       <c r="K31" s="9"/>
       <c r="L31" s="43" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="M31" s="40">
         <f>(G31+H32+I33)/COUNTIF($A$2:$A$125,F30)</f>
         <v>0.66666666666666663</v>
       </c>
       <c r="N31" s="42" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="32" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -21491,14 +21485,14 @@
       </c>
       <c r="K32" s="9"/>
       <c r="L32" s="43" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="M32" s="44">
         <f t="array" ref="M32">SUMPRODUCT(J31:J33/COUNTIF($A$2:$A$125,F30), TRANSPOSE(G34:I34)/COUNTIF($A$2:$A$125,F30))</f>
         <v>0.34666666666666668</v>
       </c>
       <c r="N32" s="45" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -21540,14 +21534,14 @@
       </c>
       <c r="K33" s="9"/>
       <c r="L33" s="43" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="M33" s="46">
         <f>(M31-M32)/(1-M32)</f>
         <v>0.48979591836734687</v>
       </c>
       <c r="N33" s="48" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="34" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -21569,7 +21563,7 @@
       </c>
       <c r="E34" s="32"/>
       <c r="F34" s="49" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="G34" s="9">
         <f t="shared" ref="G34:I34" si="18">SUM(G31:G33)</f>
@@ -21624,14 +21618,14 @@
         <v>1</v>
       </c>
       <c r="E36" s="32"/>
-      <c r="F36" s="70" t="s">
-        <v>200</v>
-      </c>
-      <c r="G36" s="71"/>
-      <c r="H36" s="71"/>
-      <c r="I36" s="71"/>
+      <c r="F36" s="68" t="s">
+        <v>198</v>
+      </c>
+      <c r="G36" s="69"/>
+      <c r="H36" s="69"/>
+      <c r="I36" s="69"/>
       <c r="L36" s="72" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="M36" s="73"/>
       <c r="N36" s="73"/>
@@ -21658,26 +21652,26 @@
         <v>9</v>
       </c>
       <c r="G37" s="53" t="s">
+        <v>177</v>
+      </c>
+      <c r="H37" s="53" t="s">
+        <v>178</v>
+      </c>
+      <c r="I37" s="53" t="s">
         <v>179</v>
       </c>
-      <c r="H37" s="53" t="s">
+      <c r="J37" s="54" t="s">
         <v>180</v>
-      </c>
-      <c r="I37" s="53" t="s">
-        <v>181</v>
-      </c>
-      <c r="J37" s="54" t="s">
-        <v>182</v>
       </c>
       <c r="K37" s="9"/>
       <c r="L37" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="M37" s="38" t="s">
+        <v>182</v>
+      </c>
+      <c r="N37" s="38" t="s">
         <v>183</v>
-      </c>
-      <c r="M37" s="38" t="s">
-        <v>184</v>
-      </c>
-      <c r="N37" s="38" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="38" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -21719,14 +21713,14 @@
       </c>
       <c r="K38" s="9"/>
       <c r="L38" s="43" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="M38" s="40">
         <f>(G38+H39+I40)/COUNTIF($A$2:$A$125,F37)</f>
         <v>0.61538461538461542</v>
       </c>
       <c r="N38" s="42" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="39" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -21768,14 +21762,14 @@
       </c>
       <c r="K39" s="9"/>
       <c r="L39" s="43" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="M39" s="44">
         <f t="array" ref="M39">SUMPRODUCT(J38:J40/COUNTIF($A$2:$A$125,F37), TRANSPOSE(G41:I41)/COUNTIF($A$2:$A$125,F37))</f>
         <v>0.3550295857988166</v>
       </c>
       <c r="N39" s="45" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="40" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -21817,14 +21811,14 @@
       </c>
       <c r="K40" s="9"/>
       <c r="L40" s="43" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="M40" s="46">
         <f>(M38-M39)/(1-M39)</f>
         <v>0.40366972477064222</v>
       </c>
       <c r="N40" s="48" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="41" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -21846,7 +21840,7 @@
       </c>
       <c r="E41" s="32"/>
       <c r="F41" s="64" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="G41" s="16">
         <f>SUM(G38:G40)</f>
@@ -21901,14 +21895,14 @@
         <v>1</v>
       </c>
       <c r="E43" s="32"/>
-      <c r="F43" s="70" t="s">
-        <v>202</v>
-      </c>
-      <c r="G43" s="71"/>
-      <c r="H43" s="71"/>
-      <c r="I43" s="71"/>
+      <c r="F43" s="68" t="s">
+        <v>200</v>
+      </c>
+      <c r="G43" s="69"/>
+      <c r="H43" s="69"/>
+      <c r="I43" s="69"/>
       <c r="L43" s="72" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="M43" s="73"/>
       <c r="N43" s="73"/>
@@ -21935,26 +21929,26 @@
         <v>43</v>
       </c>
       <c r="G44" s="51" t="s">
+        <v>177</v>
+      </c>
+      <c r="H44" s="51" t="s">
+        <v>178</v>
+      </c>
+      <c r="I44" s="51" t="s">
         <v>179</v>
       </c>
-      <c r="H44" s="51" t="s">
+      <c r="J44" s="52" t="s">
         <v>180</v>
-      </c>
-      <c r="I44" s="51" t="s">
-        <v>181</v>
-      </c>
-      <c r="J44" s="52" t="s">
-        <v>182</v>
       </c>
       <c r="K44" s="9"/>
       <c r="L44" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="M44" s="38" t="s">
+        <v>182</v>
+      </c>
+      <c r="N44" s="38" t="s">
         <v>183</v>
-      </c>
-      <c r="M44" s="38" t="s">
-        <v>184</v>
-      </c>
-      <c r="N44" s="38" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="45" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -21996,14 +21990,14 @@
       </c>
       <c r="K45" s="9"/>
       <c r="L45" s="43" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="M45" s="40">
         <f>(G45+H46+I47)/COUNTIF($A$2:$A$125,F44)</f>
         <v>1</v>
       </c>
       <c r="N45" s="42" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="46" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -22045,14 +22039,14 @@
       </c>
       <c r="K46" s="9"/>
       <c r="L46" s="43" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="M46" s="44">
         <f t="array" ref="M46">SUMPRODUCT(J45:J47/COUNTIF($A$2:$A$125,F44), TRANSPOSE(G48:I48)/COUNTIF($A$2:$A$125,F44))</f>
         <v>0.5</v>
       </c>
       <c r="N46" s="45" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="47" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -22094,14 +22088,14 @@
       </c>
       <c r="K47" s="9"/>
       <c r="L47" s="43" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="M47" s="46">
         <f>(M45-M46)/(1-M46)</f>
         <v>1</v>
       </c>
       <c r="N47" s="48" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="48" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -22123,7 +22117,7 @@
       </c>
       <c r="E48" s="32"/>
       <c r="F48" s="49" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="G48" s="9">
         <f t="shared" ref="G48:I48" si="23">SUM(G45:G47)</f>
@@ -22178,14 +22172,14 @@
         <v>0</v>
       </c>
       <c r="E50" s="32"/>
-      <c r="F50" s="70" t="s">
-        <v>204</v>
-      </c>
-      <c r="G50" s="71"/>
-      <c r="H50" s="71"/>
-      <c r="I50" s="71"/>
+      <c r="F50" s="68" t="s">
+        <v>202</v>
+      </c>
+      <c r="G50" s="69"/>
+      <c r="H50" s="69"/>
+      <c r="I50" s="69"/>
       <c r="L50" s="72" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="M50" s="73"/>
       <c r="N50" s="73"/>
@@ -22212,26 +22206,26 @@
         <v>13</v>
       </c>
       <c r="G51" s="51" t="s">
+        <v>177</v>
+      </c>
+      <c r="H51" s="51" t="s">
+        <v>178</v>
+      </c>
+      <c r="I51" s="51" t="s">
         <v>179</v>
       </c>
-      <c r="H51" s="51" t="s">
+      <c r="J51" s="52" t="s">
         <v>180</v>
-      </c>
-      <c r="I51" s="51" t="s">
-        <v>181</v>
-      </c>
-      <c r="J51" s="52" t="s">
-        <v>182</v>
       </c>
       <c r="K51" s="9"/>
       <c r="L51" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="M51" s="38" t="s">
+        <v>182</v>
+      </c>
+      <c r="N51" s="38" t="s">
         <v>183</v>
-      </c>
-      <c r="M51" s="38" t="s">
-        <v>184</v>
-      </c>
-      <c r="N51" s="38" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="52" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -22273,14 +22267,14 @@
       </c>
       <c r="K52" s="9"/>
       <c r="L52" s="43" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="M52" s="40">
         <f>(G52+H53+I54)/COUNTIF($A$2:$A$125,F51)</f>
         <v>1</v>
       </c>
       <c r="N52" s="42" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="53" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -22322,14 +22316,14 @@
       </c>
       <c r="K53" s="9"/>
       <c r="L53" s="43" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="M53" s="44">
         <f t="array" ref="M53">SUMPRODUCT(J52:J54/COUNTIF($A$2:$A$125,F51), TRANSPOSE(G55:I55)/COUNTIF($A$2:$A$125,F51))</f>
         <v>0.68000000000000016</v>
       </c>
       <c r="N53" s="45" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="54" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -22371,14 +22365,14 @@
       </c>
       <c r="K54" s="9"/>
       <c r="L54" s="43" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="M54" s="46">
         <f>(M52-M53)/(1-M53)</f>
         <v>1</v>
       </c>
       <c r="N54" s="48" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="55" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -22400,7 +22394,7 @@
       </c>
       <c r="E55" s="32"/>
       <c r="F55" s="49" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="G55" s="9">
         <f t="shared" ref="G55:I55" si="27">SUM(G52:G54)</f>
@@ -23810,6 +23804,12 @@
     <row r="1010" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L1:N1"/>
+    <mergeCell ref="F8:I8"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="F15:I15"/>
+    <mergeCell ref="L15:N15"/>
     <mergeCell ref="L22:N22"/>
     <mergeCell ref="F50:I50"/>
     <mergeCell ref="L50:N50"/>
@@ -23820,12 +23820,6 @@
     <mergeCell ref="L36:N36"/>
     <mergeCell ref="F43:I43"/>
     <mergeCell ref="L43:N43"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L1:N1"/>
-    <mergeCell ref="F8:I8"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="F15:I15"/>
-    <mergeCell ref="L15:N15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -23867,24 +23861,24 @@
         <v>1</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E1" s="32"/>
-      <c r="F1" s="70" t="s">
-        <v>176</v>
-      </c>
-      <c r="G1" s="71"/>
-      <c r="H1" s="71"/>
-      <c r="I1" s="71"/>
-      <c r="L1" s="70" t="s">
-        <v>206</v>
-      </c>
-      <c r="M1" s="71"/>
-      <c r="N1" s="71"/>
-      <c r="O1" s="71"/>
+      <c r="F1" s="68" t="s">
+        <v>174</v>
+      </c>
+      <c r="G1" s="69"/>
+      <c r="H1" s="69"/>
+      <c r="I1" s="69"/>
+      <c r="L1" s="68" t="s">
+        <v>204</v>
+      </c>
+      <c r="M1" s="69"/>
+      <c r="N1" s="69"/>
+      <c r="O1" s="69"/>
     </row>
     <row r="2" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="4" t="str">
@@ -23905,55 +23899,55 @@
       </c>
       <c r="E2" s="32"/>
       <c r="F2" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="G2" s="34" t="s">
+        <v>177</v>
+      </c>
+      <c r="H2" s="35" t="s">
         <v>178</v>
       </c>
-      <c r="G2" s="34" t="s">
+      <c r="I2" s="36" t="s">
         <v>179</v>
       </c>
-      <c r="H2" s="35" t="s">
+      <c r="J2" s="52" t="s">
         <v>180</v>
-      </c>
-      <c r="I2" s="36" t="s">
-        <v>181</v>
-      </c>
-      <c r="J2" s="52" t="s">
-        <v>182</v>
       </c>
       <c r="K2" s="9"/>
       <c r="L2" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="M2" s="51" t="s">
+        <v>177</v>
+      </c>
+      <c r="N2" s="51" t="s">
         <v>178</v>
       </c>
-      <c r="M2" s="51" t="s">
+      <c r="O2" s="51" t="s">
         <v>179</v>
-      </c>
-      <c r="N2" s="51" t="s">
-        <v>180</v>
-      </c>
-      <c r="O2" s="51" t="s">
-        <v>181</v>
       </c>
       <c r="P2" s="9"/>
       <c r="Q2" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="R2" s="51" t="s">
+        <v>177</v>
+      </c>
+      <c r="S2" s="51" t="s">
         <v>178</v>
       </c>
-      <c r="R2" s="51" t="s">
+      <c r="T2" s="51" t="s">
         <v>179</v>
-      </c>
-      <c r="S2" s="51" t="s">
-        <v>180</v>
-      </c>
-      <c r="T2" s="51" t="s">
-        <v>181</v>
       </c>
       <c r="V2" s="38" t="str">
         <f>"Metrics" &amp; " " &amp; F2</f>
         <v>Metrics Global</v>
       </c>
       <c r="W2" s="38" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="X2" s="38" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="3" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -24027,14 +24021,14 @@
       </c>
       <c r="U3" s="9"/>
       <c r="V3" s="43" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="W3" s="40">
         <f>SUMPRODUCT(G3:I5, M3:O5) /$J$6</f>
         <v>0.27272727272727271</v>
       </c>
       <c r="X3" s="42" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="4" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -24108,14 +24102,14 @@
       </c>
       <c r="U4" s="9"/>
       <c r="V4" s="43" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="W4" s="44">
         <f>SUMPRODUCT(R3:T5, M3:O5)</f>
         <v>0.46837578006409175</v>
       </c>
       <c r="X4" s="45" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="5" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -24189,14 +24183,14 @@
       </c>
       <c r="U5" s="9"/>
       <c r="V5" s="43" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="W5" s="46">
         <f>1-W3/W4</f>
         <v>0.41771696074900977</v>
       </c>
       <c r="X5" s="48" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="6" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -24218,7 +24212,7 @@
       </c>
       <c r="E6" s="32"/>
       <c r="F6" s="49" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="G6" s="9">
         <f t="shared" ref="G6:I6" si="8">SUM(G3:G5)</f>
@@ -24288,12 +24282,12 @@
         <v>1</v>
       </c>
       <c r="E8" s="32"/>
-      <c r="F8" s="70" t="s">
-        <v>192</v>
-      </c>
-      <c r="G8" s="71"/>
-      <c r="H8" s="71"/>
-      <c r="I8" s="71"/>
+      <c r="F8" s="68" t="s">
+        <v>190</v>
+      </c>
+      <c r="G8" s="69"/>
+      <c r="H8" s="69"/>
+      <c r="I8" s="69"/>
     </row>
     <row r="9" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="4" t="str">
@@ -24317,52 +24311,52 @@
         <v>4</v>
       </c>
       <c r="G9" s="51" t="s">
+        <v>177</v>
+      </c>
+      <c r="H9" s="51" t="s">
+        <v>178</v>
+      </c>
+      <c r="I9" s="51" t="s">
         <v>179</v>
       </c>
-      <c r="H9" s="51" t="s">
+      <c r="J9" s="52" t="s">
         <v>180</v>
-      </c>
-      <c r="I9" s="51" t="s">
-        <v>181</v>
-      </c>
-      <c r="J9" s="52" t="s">
-        <v>182</v>
       </c>
       <c r="K9" s="9"/>
       <c r="L9" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="M9" s="51" t="s">
+        <v>177</v>
+      </c>
+      <c r="N9" s="51" t="s">
         <v>178</v>
       </c>
-      <c r="M9" s="51" t="s">
+      <c r="O9" s="51" t="s">
         <v>179</v>
-      </c>
-      <c r="N9" s="51" t="s">
-        <v>180</v>
-      </c>
-      <c r="O9" s="51" t="s">
-        <v>181</v>
       </c>
       <c r="P9" s="9"/>
       <c r="Q9" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="R9" s="51" t="s">
+        <v>177</v>
+      </c>
+      <c r="S9" s="51" t="s">
         <v>178</v>
       </c>
-      <c r="R9" s="51" t="s">
+      <c r="T9" s="51" t="s">
         <v>179</v>
-      </c>
-      <c r="S9" s="51" t="s">
-        <v>180</v>
-      </c>
-      <c r="T9" s="51" t="s">
-        <v>181</v>
       </c>
       <c r="V9" s="38" t="str">
         <f>"Metrics" &amp; " " &amp; F9</f>
         <v>Metrics State</v>
       </c>
       <c r="W9" s="38" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="X9" s="38" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="10" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -24436,14 +24430,14 @@
       </c>
       <c r="U10" s="9"/>
       <c r="V10" s="43" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="W10" s="40">
         <f>SUMPRODUCT(G10:I12, M10:O12) /$J$13</f>
         <v>0.44444444444444442</v>
       </c>
       <c r="X10" s="42" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="11" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -24517,14 +24511,14 @@
       </c>
       <c r="U11" s="9"/>
       <c r="V11" s="43" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="W11" s="44">
         <f>SUMPRODUCT(R10:T12, M10:O12)</f>
         <v>0.58024691358024694</v>
       </c>
       <c r="X11" s="45" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="12" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -24598,14 +24592,14 @@
       </c>
       <c r="U12" s="9"/>
       <c r="V12" s="43" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="W12" s="46">
         <f>1-W10/W11</f>
         <v>0.23404255319148948</v>
       </c>
       <c r="X12" s="48" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="13" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -24627,7 +24621,7 @@
       </c>
       <c r="E13" s="32"/>
       <c r="F13" s="49" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="G13" s="9">
         <f t="shared" ref="G13:I13" si="18">SUM(G10:G12)</f>
@@ -24683,12 +24677,12 @@
         <v>0.5</v>
       </c>
       <c r="E15" s="32"/>
-      <c r="F15" s="70" t="s">
-        <v>194</v>
-      </c>
-      <c r="G15" s="71"/>
-      <c r="H15" s="71"/>
-      <c r="I15" s="71"/>
+      <c r="F15" s="68" t="s">
+        <v>192</v>
+      </c>
+      <c r="G15" s="69"/>
+      <c r="H15" s="69"/>
+      <c r="I15" s="69"/>
     </row>
     <row r="16" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="4" t="str">
@@ -24712,52 +24706,52 @@
         <v>7</v>
       </c>
       <c r="G16" s="51" t="s">
+        <v>177</v>
+      </c>
+      <c r="H16" s="51" t="s">
+        <v>178</v>
+      </c>
+      <c r="I16" s="51" t="s">
         <v>179</v>
       </c>
-      <c r="H16" s="51" t="s">
+      <c r="J16" s="52" t="s">
         <v>180</v>
-      </c>
-      <c r="I16" s="51" t="s">
-        <v>181</v>
-      </c>
-      <c r="J16" s="52" t="s">
-        <v>182</v>
       </c>
       <c r="K16" s="9"/>
       <c r="L16" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="M16" s="51" t="s">
+        <v>177</v>
+      </c>
+      <c r="N16" s="51" t="s">
         <v>178</v>
       </c>
-      <c r="M16" s="51" t="s">
+      <c r="O16" s="51" t="s">
         <v>179</v>
-      </c>
-      <c r="N16" s="51" t="s">
-        <v>180</v>
-      </c>
-      <c r="O16" s="51" t="s">
-        <v>181</v>
       </c>
       <c r="P16" s="9"/>
       <c r="Q16" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="R16" s="51" t="s">
+        <v>177</v>
+      </c>
+      <c r="S16" s="51" t="s">
         <v>178</v>
       </c>
-      <c r="R16" s="51" t="s">
+      <c r="T16" s="51" t="s">
         <v>179</v>
-      </c>
-      <c r="S16" s="51" t="s">
-        <v>180</v>
-      </c>
-      <c r="T16" s="51" t="s">
-        <v>181</v>
       </c>
       <c r="V16" s="38" t="str">
         <f>"Metrics" &amp; " " &amp; F16</f>
         <v>Metrics Transition</v>
       </c>
       <c r="W16" s="38" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="X16" s="38" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="17" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -24831,14 +24825,14 @@
       </c>
       <c r="U17" s="9"/>
       <c r="V17" s="43" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="W17" s="40">
         <f>SUMPRODUCT(G17:I19, M17:O19) /$J$20</f>
         <v>0.35714285714285715</v>
       </c>
       <c r="X17" s="42" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="18" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -24912,14 +24906,14 @@
       </c>
       <c r="U18" s="9"/>
       <c r="V18" s="43" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="W18" s="44">
         <f>SUMPRODUCT(R17:T19, M17:O19)</f>
         <v>0.48185941043083896</v>
       </c>
       <c r="X18" s="45" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="19" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -24993,14 +24987,14 @@
       </c>
       <c r="U19" s="9"/>
       <c r="V19" s="43" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="W19" s="46">
         <f>1-W17/W18</f>
         <v>0.25882352941176467</v>
       </c>
       <c r="X19" s="48" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="20" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -25022,7 +25016,7 @@
       </c>
       <c r="E20" s="32"/>
       <c r="F20" s="49" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="G20" s="9">
         <f t="shared" ref="G20:I20" si="28">SUM(G17:G19)</f>
@@ -25078,12 +25072,12 @@
         <v>0</v>
       </c>
       <c r="E22" s="32"/>
-      <c r="F22" s="70" t="s">
-        <v>196</v>
-      </c>
-      <c r="G22" s="71"/>
-      <c r="H22" s="71"/>
-      <c r="I22" s="71"/>
+      <c r="F22" s="68" t="s">
+        <v>194</v>
+      </c>
+      <c r="G22" s="69"/>
+      <c r="H22" s="69"/>
+      <c r="I22" s="69"/>
     </row>
     <row r="23" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="4" t="str">
@@ -25107,52 +25101,52 @@
         <v>11</v>
       </c>
       <c r="G23" s="51" t="s">
+        <v>177</v>
+      </c>
+      <c r="H23" s="51" t="s">
+        <v>178</v>
+      </c>
+      <c r="I23" s="51" t="s">
         <v>179</v>
       </c>
-      <c r="H23" s="51" t="s">
+      <c r="J23" s="52" t="s">
         <v>180</v>
-      </c>
-      <c r="I23" s="51" t="s">
-        <v>181</v>
-      </c>
-      <c r="J23" s="52" t="s">
-        <v>182</v>
       </c>
       <c r="K23" s="9"/>
       <c r="L23" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="M23" s="51" t="s">
+        <v>177</v>
+      </c>
+      <c r="N23" s="51" t="s">
         <v>178</v>
       </c>
-      <c r="M23" s="51" t="s">
+      <c r="O23" s="51" t="s">
         <v>179</v>
-      </c>
-      <c r="N23" s="51" t="s">
-        <v>180</v>
-      </c>
-      <c r="O23" s="51" t="s">
-        <v>181</v>
       </c>
       <c r="P23" s="9"/>
       <c r="Q23" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="R23" s="51" t="s">
+        <v>177</v>
+      </c>
+      <c r="S23" s="51" t="s">
         <v>178</v>
       </c>
-      <c r="R23" s="51" t="s">
+      <c r="T23" s="51" t="s">
         <v>179</v>
-      </c>
-      <c r="S23" s="51" t="s">
-        <v>180</v>
-      </c>
-      <c r="T23" s="51" t="s">
-        <v>181</v>
       </c>
       <c r="V23" s="38" t="str">
         <f>"Metrics" &amp; " " &amp; F23</f>
         <v>Metrics Composite State</v>
       </c>
       <c r="W23" s="38" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="X23" s="38" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="24" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -25226,14 +25220,14 @@
       </c>
       <c r="U24" s="9"/>
       <c r="V24" s="43" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="W24" s="40">
         <f>SUMPRODUCT(G24:I26, M24:O26) /$J$27</f>
         <v>0</v>
       </c>
       <c r="X24" s="42" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="25" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -25307,14 +25301,14 @@
       </c>
       <c r="U25" s="9"/>
       <c r="V25" s="43" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="W25" s="44">
         <f>SUMPRODUCT(R24:T26, M24:O26)</f>
         <v>0.44444444444444442</v>
       </c>
       <c r="X25" s="45" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="26" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -25388,14 +25382,14 @@
       </c>
       <c r="U26" s="9"/>
       <c r="V26" s="43" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="W26" s="46">
         <f>1-W24/W25</f>
         <v>1</v>
       </c>
       <c r="X26" s="48" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="27" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -25417,7 +25411,7 @@
       </c>
       <c r="E27" s="32"/>
       <c r="F27" s="49" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="G27" s="9">
         <f t="shared" ref="G27:I27" si="38">SUM(G24:G26)</f>
@@ -25473,12 +25467,12 @@
         <v>1</v>
       </c>
       <c r="E29" s="32"/>
-      <c r="F29" s="70" t="s">
-        <v>198</v>
-      </c>
-      <c r="G29" s="71"/>
-      <c r="H29" s="71"/>
-      <c r="I29" s="71"/>
+      <c r="F29" s="68" t="s">
+        <v>196</v>
+      </c>
+      <c r="G29" s="69"/>
+      <c r="H29" s="69"/>
+      <c r="I29" s="69"/>
     </row>
     <row r="30" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="4" t="str">
@@ -25502,52 +25496,52 @@
         <v>21</v>
       </c>
       <c r="G30" s="51" t="s">
+        <v>177</v>
+      </c>
+      <c r="H30" s="51" t="s">
+        <v>178</v>
+      </c>
+      <c r="I30" s="51" t="s">
         <v>179</v>
       </c>
-      <c r="H30" s="51" t="s">
+      <c r="J30" s="52" t="s">
         <v>180</v>
-      </c>
-      <c r="I30" s="51" t="s">
-        <v>181</v>
-      </c>
-      <c r="J30" s="52" t="s">
-        <v>182</v>
       </c>
       <c r="K30" s="9"/>
       <c r="L30" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="M30" s="51">
+        <v>0</v>
+      </c>
+      <c r="N30" s="51" t="s">
         <v>178</v>
       </c>
-      <c r="M30" s="51">
-        <v>0</v>
-      </c>
-      <c r="N30" s="51" t="s">
-        <v>180</v>
-      </c>
       <c r="O30" s="51" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="P30" s="9"/>
       <c r="Q30" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="R30" s="51" t="s">
+        <v>177</v>
+      </c>
+      <c r="S30" s="51" t="s">
         <v>178</v>
       </c>
-      <c r="R30" s="51" t="s">
+      <c r="T30" s="51" t="s">
         <v>179</v>
-      </c>
-      <c r="S30" s="51" t="s">
-        <v>180</v>
-      </c>
-      <c r="T30" s="51" t="s">
-        <v>181</v>
       </c>
       <c r="V30" s="38" t="str">
         <f>"Metrics" &amp; " " &amp; F30</f>
         <v>Metrics Guard</v>
       </c>
       <c r="W30" s="38" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="X30" s="38" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="31" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -25621,14 +25615,14 @@
       </c>
       <c r="U31" s="9"/>
       <c r="V31" s="43" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="W31" s="40">
         <f>SUMPRODUCT(G31:I33, M31:O33) /$J$34</f>
         <v>0.16666666666666666</v>
       </c>
       <c r="X31" s="42" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="32" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -25702,14 +25696,14 @@
       </c>
       <c r="U32" s="9"/>
       <c r="V32" s="43" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="W32" s="44">
         <f>SUMPRODUCT(R31:T33, M31:O33)</f>
         <v>0.44222222222222218</v>
       </c>
       <c r="X32" s="45" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="33" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -25783,14 +25777,14 @@
       </c>
       <c r="U33" s="9"/>
       <c r="V33" s="43" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="W33" s="46">
         <f>1-W31/W32</f>
         <v>0.62311557788944727</v>
       </c>
       <c r="X33" s="48" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="34" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -25812,7 +25806,7 @@
       </c>
       <c r="E34" s="32"/>
       <c r="F34" s="49" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="G34" s="9">
         <f t="shared" ref="G34:I34" si="48">SUM(G31:G33)</f>
@@ -25868,12 +25862,12 @@
         <v>1</v>
       </c>
       <c r="E36" s="32"/>
-      <c r="F36" s="70" t="s">
-        <v>200</v>
-      </c>
-      <c r="G36" s="71"/>
-      <c r="H36" s="71"/>
-      <c r="I36" s="71"/>
+      <c r="F36" s="68" t="s">
+        <v>198</v>
+      </c>
+      <c r="G36" s="69"/>
+      <c r="H36" s="69"/>
+      <c r="I36" s="69"/>
     </row>
     <row r="37" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="4" t="str">
@@ -25897,42 +25891,42 @@
         <v>9</v>
       </c>
       <c r="G37" s="53" t="s">
+        <v>177</v>
+      </c>
+      <c r="H37" s="53" t="s">
+        <v>178</v>
+      </c>
+      <c r="I37" s="53" t="s">
         <v>179</v>
       </c>
-      <c r="H37" s="53" t="s">
+      <c r="J37" s="54" t="s">
         <v>180</v>
-      </c>
-      <c r="I37" s="53" t="s">
-        <v>181</v>
-      </c>
-      <c r="J37" s="54" t="s">
-        <v>182</v>
       </c>
       <c r="K37" s="9"/>
       <c r="L37" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="M37" s="51">
+        <v>0</v>
+      </c>
+      <c r="N37" s="51" t="s">
         <v>178</v>
       </c>
-      <c r="M37" s="51">
-        <v>0</v>
-      </c>
-      <c r="N37" s="51" t="s">
-        <v>180</v>
-      </c>
       <c r="O37" s="51" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="P37" s="9"/>
       <c r="Q37" s="16" t="s">
+        <v>176</v>
+      </c>
+      <c r="R37" s="66" t="s">
+        <v>177</v>
+      </c>
+      <c r="S37" s="66" t="s">
         <v>178</v>
       </c>
-      <c r="R37" s="66" t="s">
+      <c r="T37" s="66" t="s">
         <v>179</v>
-      </c>
-      <c r="S37" s="66" t="s">
-        <v>180</v>
-      </c>
-      <c r="T37" s="66" t="s">
-        <v>181</v>
       </c>
       <c r="U37" s="9"/>
       <c r="V37" s="38" t="str">
@@ -25940,10 +25934,10 @@
         <v>Metrics Action</v>
       </c>
       <c r="W37" s="38" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="X37" s="38" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="38" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -26017,14 +26011,14 @@
       </c>
       <c r="U38" s="9"/>
       <c r="V38" s="43" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="W38" s="40">
         <f>SUMPRODUCT(G38:I40, M38:O40) /$J$41</f>
         <v>0.21428571428571427</v>
       </c>
       <c r="X38" s="42" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="39" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -26098,14 +26092,14 @@
       </c>
       <c r="U39" s="9"/>
       <c r="V39" s="43" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="W39" s="44">
         <f>SUMPRODUCT(R38:T40, M38:O40)</f>
         <v>0.33673469387755106</v>
       </c>
       <c r="X39" s="45" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="40" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -26179,14 +26173,14 @@
       </c>
       <c r="U40" s="9"/>
       <c r="V40" s="43" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="W40" s="46">
         <f>1-W38/W39</f>
         <v>0.36363636363636376</v>
       </c>
       <c r="X40" s="48" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="41" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -26208,7 +26202,7 @@
       </c>
       <c r="E41" s="32"/>
       <c r="F41" s="64" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="G41" s="16">
         <f>SUM(G38:G40)</f>
@@ -26264,12 +26258,12 @@
         <v>1</v>
       </c>
       <c r="E43" s="32"/>
-      <c r="F43" s="70" t="s">
-        <v>202</v>
-      </c>
-      <c r="G43" s="71"/>
-      <c r="H43" s="71"/>
-      <c r="I43" s="71"/>
+      <c r="F43" s="68" t="s">
+        <v>200</v>
+      </c>
+      <c r="G43" s="69"/>
+      <c r="H43" s="69"/>
+      <c r="I43" s="69"/>
     </row>
     <row r="44" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="4" t="str">
@@ -26293,52 +26287,52 @@
         <v>43</v>
       </c>
       <c r="G44" s="51" t="s">
+        <v>177</v>
+      </c>
+      <c r="H44" s="51" t="s">
+        <v>178</v>
+      </c>
+      <c r="I44" s="51" t="s">
         <v>179</v>
       </c>
-      <c r="H44" s="51" t="s">
+      <c r="J44" s="52" t="s">
         <v>180</v>
-      </c>
-      <c r="I44" s="51" t="s">
-        <v>181</v>
-      </c>
-      <c r="J44" s="52" t="s">
-        <v>182</v>
       </c>
       <c r="K44" s="9"/>
       <c r="L44" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="M44" s="51" t="s">
+        <v>177</v>
+      </c>
+      <c r="N44" s="51" t="s">
         <v>178</v>
       </c>
-      <c r="M44" s="51" t="s">
+      <c r="O44" s="51" t="s">
         <v>179</v>
-      </c>
-      <c r="N44" s="51" t="s">
-        <v>180</v>
-      </c>
-      <c r="O44" s="51" t="s">
-        <v>181</v>
       </c>
       <c r="P44" s="9"/>
       <c r="Q44" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="R44" s="51" t="s">
+        <v>177</v>
+      </c>
+      <c r="S44" s="51" t="s">
         <v>178</v>
       </c>
-      <c r="R44" s="51" t="s">
+      <c r="T44" s="51" t="s">
         <v>179</v>
-      </c>
-      <c r="S44" s="51" t="s">
-        <v>180</v>
-      </c>
-      <c r="T44" s="51" t="s">
-        <v>181</v>
       </c>
       <c r="V44" s="38" t="str">
         <f>"Metrics" &amp; " " &amp; F44</f>
         <v>Metrics History State</v>
       </c>
       <c r="W44" s="38" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="X44" s="38" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="45" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -26412,14 +26406,14 @@
       </c>
       <c r="U45" s="9"/>
       <c r="V45" s="43" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="W45" s="40">
         <f>SUMPRODUCT(G45:I47, M45:O47) /$J$48</f>
         <v>0</v>
       </c>
       <c r="X45" s="42" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="46" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -26493,14 +26487,14 @@
       </c>
       <c r="U46" s="9"/>
       <c r="V46" s="43" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="W46" s="44">
         <f>SUMPRODUCT(R45:T47, M45:O47)</f>
         <v>0.5</v>
       </c>
       <c r="X46" s="45" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="47" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -26574,14 +26568,14 @@
       </c>
       <c r="U47" s="9"/>
       <c r="V47" s="43" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="W47" s="46">
         <f>1-W45/W46</f>
         <v>1</v>
       </c>
       <c r="X47" s="48" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="48" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -26603,7 +26597,7 @@
       </c>
       <c r="E48" s="32"/>
       <c r="F48" s="49" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="G48" s="9">
         <f t="shared" ref="G48:I48" si="65">SUM(G45:G47)</f>
@@ -26659,12 +26653,12 @@
         <v>0</v>
       </c>
       <c r="E50" s="32"/>
-      <c r="F50" s="70" t="s">
-        <v>204</v>
-      </c>
-      <c r="G50" s="71"/>
-      <c r="H50" s="71"/>
-      <c r="I50" s="71"/>
+      <c r="F50" s="68" t="s">
+        <v>202</v>
+      </c>
+      <c r="G50" s="69"/>
+      <c r="H50" s="69"/>
+      <c r="I50" s="69"/>
     </row>
     <row r="51" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="4" t="str">
@@ -26688,52 +26682,52 @@
         <v>13</v>
       </c>
       <c r="G51" s="51" t="s">
+        <v>177</v>
+      </c>
+      <c r="H51" s="51" t="s">
+        <v>178</v>
+      </c>
+      <c r="I51" s="51" t="s">
         <v>179</v>
       </c>
-      <c r="H51" s="51" t="s">
+      <c r="J51" s="52" t="s">
         <v>180</v>
-      </c>
-      <c r="I51" s="51" t="s">
-        <v>181</v>
-      </c>
-      <c r="J51" s="52" t="s">
-        <v>182</v>
       </c>
       <c r="K51" s="9"/>
       <c r="L51" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="M51" s="51" t="s">
+        <v>177</v>
+      </c>
+      <c r="N51" s="51" t="s">
         <v>178</v>
       </c>
-      <c r="M51" s="51" t="s">
+      <c r="O51" s="51" t="s">
         <v>179</v>
-      </c>
-      <c r="N51" s="51" t="s">
-        <v>180</v>
-      </c>
-      <c r="O51" s="51" t="s">
-        <v>181</v>
       </c>
       <c r="P51" s="9"/>
       <c r="Q51" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="R51" s="51" t="s">
+        <v>177</v>
+      </c>
+      <c r="S51" s="51" t="s">
         <v>178</v>
       </c>
-      <c r="R51" s="51" t="s">
+      <c r="T51" s="51" t="s">
         <v>179</v>
-      </c>
-      <c r="S51" s="51" t="s">
-        <v>180</v>
-      </c>
-      <c r="T51" s="51" t="s">
-        <v>181</v>
       </c>
       <c r="V51" s="38" t="str">
         <f>"Metrics" &amp; " " &amp; F51</f>
         <v>Metrics Region</v>
       </c>
       <c r="W51" s="38" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="X51" s="38" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="52" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -26807,14 +26801,14 @@
       </c>
       <c r="U52" s="9"/>
       <c r="V52" s="43" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="W52" s="40">
         <f>SUMPRODUCT(G52:I54, M52:O54) /$J$55</f>
         <v>0</v>
       </c>
       <c r="X52" s="42" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="53" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -26888,14 +26882,14 @@
       </c>
       <c r="U53" s="9"/>
       <c r="V53" s="43" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="W53" s="44">
         <f>SUMPRODUCT(R52:T54, M52:O54)</f>
         <v>0.32000000000000006</v>
       </c>
       <c r="X53" s="45" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="54" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -26969,14 +26963,14 @@
       </c>
       <c r="U54" s="9"/>
       <c r="V54" s="43" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="W54" s="46">
         <f>1-W52/W53</f>
         <v>1</v>
       </c>
       <c r="X54" s="48" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="55" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -26998,7 +26992,7 @@
       </c>
       <c r="E55" s="32"/>
       <c r="F55" s="49" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="G55" s="9">
         <f t="shared" ref="G55:I55" si="75">SUM(G52:G54)</f>
